--- a/02-governance-gap-analysis/governance-gap-analysis.xlsx
+++ b/02-governance-gap-analysis/governance-gap-analysis.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>No formal cross-functional venue to align business priorities with security investments.</t>
+          <t>No formal cross-functional venue to align business priorities with security investments. Remediation: Establish the IT Steering Committee defined in the Governance Organizational Structure (Activity 3).</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>The board lacks proactive visibility into operational risk postures and systemic gaps.</t>
+          <t>The board lacks proactive visibility into operational risk postures and systemic gaps. Remediation: Activate board-level oversight through the Board Risk &amp; Security Committee, Audit &amp; Compliance Committee, and Technology &amp; Innovation Committee defined in the Governance Organizational Structure (Activity 3).</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
